--- a/scripts/portfolio.xlsx
+++ b/scripts/portfolio.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,27 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EBF3FB"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -60,17 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,175 +413,210 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>티커</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>시장(US/KR)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>진입가</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>주수</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>진입일</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>스톱로스</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>목표가</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>AAPL</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Apple Inc.</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DOW</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dow Inc.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>180</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>250</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>39.36</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>NVIDIA Corp.</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MPC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Marathon Petroleum</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>180</v>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>AI 반도체</t>
-        </is>
-      </c>
+      <c r="D3" t="n">
+        <v>244.78</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>005930.KS</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>삼성전자</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>80000</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>72000</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>100000</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>OXY</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Occidental Petroleum</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>61.29</v>
+      </c>
+      <c r="E4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TPL</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Texas Pacific Land</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>536.27</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PSX</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Phillips 66</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>184.52</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scripts/portfolio.xlsx
+++ b/scripts/portfolio.xlsx
@@ -487,12 +487,9 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+          <t>2026-03-27</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -518,12 +515,9 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+          <t>2026-03-25</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -549,12 +543,9 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+          <t>2026-03-25</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -580,12 +571,9 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+          <t>2026-03-25</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -611,12 +599,9 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+          <t>2026-03-25</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
